--- a/03 - Data Acquisition/notebooks/outputs/part2/task3_results.xlsx
+++ b/03 - Data Acquisition/notebooks/outputs/part2/task3_results.xlsx
@@ -58,7 +58,7 @@
     <t>2010-08-17T09:43:38Z</t>
   </si>
   <si>
-    <t>Generated on: 2026-03-05 02:42:58.981425</t>
+    <t>Generated on: 2026-03-06 15:31:17.820450</t>
   </si>
 </sst>
 </file>
@@ -90,7 +90,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -98,13 +98,33 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -402,91 +422,96 @@
   <dimension ref="A1:F6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="6" width="20.7109375" customWidth="1"/>
+    <col min="1" max="1" width="22.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="21.7109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="30.7109375" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="2" spans="1:6">
-      <c r="A2" t="s">
+      <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B2">
-        <v>194001</v>
-      </c>
-      <c r="C2">
-        <v>75215</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="B2" s="1">
+        <v>194012</v>
+      </c>
+      <c r="C2" s="1">
+        <v>75218</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E2">
-        <v>3589</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="E2" s="1">
+        <v>3624</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:6">
-      <c r="A3" t="s">
+      <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B3">
-        <v>97967</v>
-      </c>
-      <c r="C3">
-        <v>27072</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="B3" s="1">
+        <v>97996</v>
+      </c>
+      <c r="C3" s="1">
+        <v>27089</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E3">
-        <v>18083</v>
-      </c>
-      <c r="F3" t="s">
+      <c r="E3" s="1">
+        <v>18094</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" t="s">
+      <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B4">
-        <v>65292</v>
-      </c>
-      <c r="C4">
-        <v>26747</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="B4" s="1">
+        <v>65306</v>
+      </c>
+      <c r="C4" s="1">
+        <v>26750</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E4">
-        <v>2143</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="E4" s="1">
+        <v>2134</v>
+      </c>
+      <c r="F4" s="1" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" t="s">
+      <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
     </row>
